--- a/apex/apex_legends.xlsx
+++ b/apex/apex_legends.xlsx
@@ -1,34 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\John\Documents\John\AUTOvalorant\apex\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\inGameSelection\apex\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9334E5D-AF5F-4D71-9125-13BE498C249C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD06403-E8DA-4047-857A-C7D9C666BC45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41490" yWindow="405" windowWidth="28110" windowHeight="19785" xr2:uid="{C170FA88-9792-427E-A191-8EBCAC680A35}"/>
+    <workbookView xWindow="345" yWindow="390" windowWidth="28800" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$H$1</definedName>
-  </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="36">
+  <si>
+    <t>order</t>
+  </si>
   <si>
     <t>legends</t>
   </si>
@@ -42,110 +37,115 @@
     <t>yindex</t>
   </si>
   <si>
+    <t>bangalore</t>
+  </si>
+  <si>
+    <t>assault</t>
+  </si>
+  <si>
+    <t>fuse</t>
+  </si>
+  <si>
     <t>ash</t>
   </si>
   <si>
-    <t>bangalore</t>
+    <t>maggie</t>
+  </si>
+  <si>
+    <t>ballistic</t>
+  </si>
+  <si>
+    <t>pathfinder</t>
+  </si>
+  <si>
+    <t>skirmisher</t>
+  </si>
+  <si>
+    <t>wraith</t>
+  </si>
+  <si>
+    <t>octane</t>
+  </si>
+  <si>
+    <t>revenant</t>
+  </si>
+  <si>
+    <t>horizon</t>
+  </si>
+  <si>
+    <t>valkyrie</t>
+  </si>
+  <si>
+    <t>alter</t>
   </si>
   <si>
     <t>bloodhound</t>
   </si>
   <si>
-    <t>fuse</t>
+    <t>recon</t>
+  </si>
+  <si>
+    <t>crypto</t>
+  </si>
+  <si>
+    <t>seer</t>
+  </si>
+  <si>
+    <t>vantage</t>
   </si>
   <si>
     <t>gibraltar</t>
   </si>
   <si>
-    <t>horizon</t>
+    <t>support</t>
   </si>
   <si>
     <t>lifeline</t>
   </si>
   <si>
-    <t>maggie</t>
-  </si>
-  <si>
-    <t>pathfinder</t>
+    <t>mirage</t>
+  </si>
+  <si>
+    <t>loba</t>
+  </si>
+  <si>
+    <t>newcastle</t>
+  </si>
+  <si>
+    <t>conduit</t>
+  </si>
+  <si>
+    <t>caustic</t>
+  </si>
+  <si>
+    <t>controller</t>
+  </si>
+  <si>
+    <t>wattson</t>
   </si>
   <si>
     <t>rampart</t>
   </si>
   <si>
-    <t>seer</t>
-  </si>
-  <si>
-    <t>wraith</t>
-  </si>
-  <si>
-    <t>conduit</t>
-  </si>
-  <si>
-    <t>assault</t>
-  </si>
-  <si>
-    <t>skirmisher</t>
-  </si>
-  <si>
-    <t>revenant</t>
-  </si>
-  <si>
-    <t>recon</t>
-  </si>
-  <si>
-    <t>vantage</t>
-  </si>
-  <si>
-    <t>support</t>
-  </si>
-  <si>
-    <t>controller</t>
-  </si>
-  <si>
-    <t>caustic</t>
-  </si>
-  <si>
     <t>catalyst</t>
-  </si>
-  <si>
-    <t>ballistic</t>
-  </si>
-  <si>
-    <t>octane</t>
-  </si>
-  <si>
-    <t>valkyrie</t>
-  </si>
-  <si>
-    <t>crypto</t>
-  </si>
-  <si>
-    <t>loba</t>
-  </si>
-  <si>
-    <t>mirage</t>
-  </si>
-  <si>
-    <t>newcastle</t>
-  </si>
-  <si>
-    <t>wattson</t>
-  </si>
-  <si>
-    <t>order</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -156,7 +156,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -164,18 +164,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -198,44 +216,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -262,32 +280,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -314,24 +314,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -343,168 +325,189 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCA5C375-D406-468A-8915-D589DE784926}">
-  <dimension ref="A1:E26"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="5.375" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E27"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -515,10 +518,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>626</v>
+        <v>547</v>
       </c>
       <c r="E2">
         <v>948</v>
@@ -532,10 +535,10 @@
         <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D3">
-        <v>730</v>
+        <v>683</v>
       </c>
       <c r="E3">
         <v>948</v>
@@ -546,13 +549,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D4">
-        <v>840</v>
+        <v>806</v>
       </c>
       <c r="E4">
         <v>948</v>
@@ -563,13 +566,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D5">
-        <v>944</v>
+        <v>861</v>
       </c>
       <c r="E5">
         <v>948</v>
@@ -580,13 +583,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="D6">
-        <v>1060</v>
+        <v>993</v>
       </c>
       <c r="E6">
         <v>948</v>
@@ -597,13 +600,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" t="s">
-        <v>18</v>
-      </c>
       <c r="D7">
-        <v>1283</v>
+        <v>1189</v>
       </c>
       <c r="E7">
         <v>948</v>
@@ -614,13 +617,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D8">
-        <v>1390</v>
+        <v>1338</v>
       </c>
       <c r="E8">
         <v>948</v>
@@ -631,13 +634,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>1478</v>
+        <v>1426</v>
       </c>
       <c r="E9">
         <v>948</v>
@@ -648,13 +651,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D10">
-        <v>1598</v>
+        <v>1531</v>
       </c>
       <c r="E10">
         <v>948</v>
@@ -665,13 +668,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C11" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D11">
-        <v>1710</v>
+        <v>1639</v>
       </c>
       <c r="E11">
         <v>948</v>
@@ -682,13 +685,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D12">
-        <v>1829</v>
+        <v>1804</v>
       </c>
       <c r="E12">
         <v>948</v>
@@ -699,16 +702,16 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D13">
-        <v>409</v>
+        <v>1870</v>
       </c>
       <c r="E13">
-        <v>1134</v>
+        <v>948</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -716,13 +719,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
       </c>
       <c r="D14">
-        <v>525</v>
+        <v>393</v>
       </c>
       <c r="E14">
         <v>1134</v>
@@ -733,13 +736,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15">
-        <v>630</v>
+        <v>508</v>
       </c>
       <c r="E15">
         <v>1134</v>
@@ -750,13 +753,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16">
-        <v>736</v>
+        <v>631</v>
       </c>
       <c r="E16">
         <v>1134</v>
@@ -767,13 +770,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D17">
-        <v>972</v>
+        <v>735</v>
       </c>
       <c r="E17">
         <v>1134</v>
@@ -784,13 +787,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D18">
-        <v>1061</v>
+        <v>983</v>
       </c>
       <c r="E18">
         <v>1134</v>
@@ -801,13 +804,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D19">
-        <v>1173</v>
+        <v>1030</v>
       </c>
       <c r="E19">
         <v>1134</v>
@@ -818,13 +821,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D20">
-        <v>1282</v>
+        <v>1130</v>
       </c>
       <c r="E20">
         <v>1134</v>
@@ -835,13 +838,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D21">
-        <v>1395</v>
+        <v>1273</v>
       </c>
       <c r="E21">
         <v>1134</v>
@@ -852,13 +855,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D22">
-        <v>1507</v>
+        <v>1354</v>
       </c>
       <c r="E22">
         <v>1134</v>
@@ -869,13 +872,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D23">
-        <v>1735</v>
+        <v>1468</v>
       </c>
       <c r="E23">
         <v>1134</v>
@@ -886,13 +889,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D24">
-        <v>1846</v>
+        <v>1716</v>
       </c>
       <c r="E24">
         <v>1134</v>
@@ -903,13 +906,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D25">
-        <v>1961</v>
+        <v>1832</v>
       </c>
       <c r="E25">
         <v>1134</v>
@@ -920,25 +923,36 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D26">
-        <v>2056</v>
+        <v>1937</v>
       </c>
       <c r="E26">
         <v>1134</v>
       </c>
     </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27">
+        <v>2060</v>
+      </c>
+      <c r="E27">
+        <v>1134</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{BCA5C375-D406-468A-8915-D589DE784926}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E26">
-      <sortCondition ref="A1"/>
-    </sortState>
-  </autoFilter>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>